--- a/data/processed/harmonization/Carbon__Mineral-associated_organic_matter_carbon/10.15485_3024414/10.15485_3024414_soil_Carbon__Mineral-associated_organic_matter_carbon.xlsx
+++ b/data/processed/harmonization/Carbon__Mineral-associated_organic_matter_carbon/10.15485_3024414/10.15485_3024414_soil_Carbon__Mineral-associated_organic_matter_carbon.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Control:2</t>
+          <t>Control:1:80-90</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -566,12 +566,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Control:6</t>
+          <t>Control:1:40-50</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Control:9</t>
+          <t>Control:1:10-20</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Warmed:12</t>
+          <t>Warmed:2:80-90</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Warmed:16</t>
+          <t>Warmed:2:40-50</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -758,12 +758,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Warmed:19</t>
+          <t>Warmed:2:10-20</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Control:22</t>
+          <t>Control:3:80-90</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Control:26</t>
+          <t>Control:3:40-50</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -902,12 +902,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Control:29</t>
+          <t>Control:3:10-20</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -950,12 +950,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Warmed:32</t>
+          <t>Warmed:4:80-90</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Warmed:36</t>
+          <t>Warmed:4:40-50</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Warmed:39</t>
+          <t>Warmed:4:10-20</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Control:42</t>
+          <t>Control:5:80-90</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Control:46</t>
+          <t>Control:5:40-50</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Control:49</t>
+          <t>Control:5:10-20</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Warmed:52</t>
+          <t>Warmed:6:80-90</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Warmed:56</t>
+          <t>Warmed:6:40-50</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Warmed:59</t>
+          <t>Warmed:6:10-20</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Treatment:ID</t>
+          <t>Treatment:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
